--- a/documents/Project_Information/Architecture & Interface Dictionary.xlsx
+++ b/documents/Project_Information/Architecture & Interface Dictionary.xlsx
@@ -21,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +58,10 @@
       <b val="1"/>
       <i val="1"/>
       <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -253,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -343,6 +349,16 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -832,9 +848,15 @@
           <t>Student Name Here</t>
         </is>
       </c>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="34" t="n"/>
-      <c r="F5" s="15" t="n"/>
+      <c r="D5" s="38" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E5" s="38" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="6" ht="15.6" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -1939,7 +1961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="26.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -2035,477 +2057,920 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="4.9" customHeight="1" thickBot="1">
-      <c r="B8" t="inlineStr">
+    <row r="8" ht="4.9" customHeight="1" thickBot="1"/>
+    <row r="9" customFormat="1" s="6">
+      <c r="A9" s="39">
+        <f>B1</f>
+        <v/>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>SW Track Controller</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>Commanded Speed</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>int m/s (per block)</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>Speed command, in whole m/s, to encode into each block's track circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="1" s="6">
+      <c r="A10" s="39">
+        <f>A9</f>
+        <v/>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr">
+        <is>
+          <t>block_id (per block)</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="inlineStr">
+        <is>
+          <t>Block up to which a train in this block may travel; encoded into the block's track circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="1" s="6">
+      <c r="A11" s="39">
+        <f>A10</f>
+        <v/>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>Switch Position Command</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>enum (Normal/Reverse)</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>Commanded position for each switch machine. The Track Model applies it and never chooses a position</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="1" s="6">
+      <c r="A12" s="39">
+        <f>A11</f>
+        <v/>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>Signal Light Color Command</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>enum (Green/Yellow/Red/SuperGreen)</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>Colour to display on each wayside signal light. Lights stand on the block right before each switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="1" s="6">
+      <c r="A13" s="39">
+        <f>A12</f>
+        <v/>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>Crossing Gate Command</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>bool (gate closed)</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="inlineStr">
+        <is>
+          <t>Commanded state of each railway crossing gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="1" s="6">
+      <c r="A14" s="39">
+        <f>A13</f>
+        <v/>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>Heater Command</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>bool (on/off, per section)</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>Command to turn the track heaters in each section on or off</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customFormat="1" s="6">
+      <c r="A15" s="39">
+        <f>A14</f>
+        <v/>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>Train Position</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>block_id, offset (m) (per train)</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>Block and metre-offset into it. Offset &gt;= block length moves the train to the next block along the current switch positions; a negative offset moves it back. Drives block occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A16" s="39">
+        <f>A15</f>
+        <v/>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>Actual Speed</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>m/s (signed, per train)</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>Train speed; a train stopped at a station can board passengers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="39">
+        <f>A16</f>
+        <v/>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>Block Change Event</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>bool (per train)</t>
+        </is>
+      </c>
+      <c r="E17" s="41" t="inlineStr">
+        <is>
+          <t>Recorded only; it follows the Track Model's own block change</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A18" s="39">
+        <f>A17</f>
+        <v/>
+      </c>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>Passenger Capacity</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>int (per train)</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>Seats the train can still fill; bounds Passengers Boarded</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16.15" customHeight="1" thickBot="1">
+      <c r="A19" s="39">
+        <f>A18</f>
+        <v/>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>Environment (UI)</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>Ambient Temperature</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="inlineStr">
+        <is>
+          <t>degrees C</t>
+        </is>
+      </c>
+      <c r="E19" s="41" t="inlineStr">
+        <is>
+          <t>Outside air temperature used to control the track heater (entered in degrees F on the UI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4.9" customHeight="1" thickBot="1">
+      <c r="A20" s="39">
+        <f>A19</f>
+        <v/>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>Environment (UI)</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>Track Layout</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr">
+        <is>
+          <t>JSON file</t>
+        </is>
+      </c>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>Line layout loaded at startup: blocks, length, grade (%), speed limit (km/h), elevation, stations, switches, crossings, and the direction of travel per block (next_blocks). Converted to degrees and m/s on read</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30.75" customHeight="1">
+      <c r="A21" s="39">
+        <f>A20</f>
+        <v/>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>Track Model UI (Murphy)</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Block Failure</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>enum (None/Broken Rail/Track Circuit/Power)</t>
+        </is>
+      </c>
+      <c r="E21" s="41" t="inlineStr">
+        <is>
+          <t>Failure injected on a block from the Track Model UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39">
+        <f>A21</f>
+        <v/>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>"Database"</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>Track Model</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="41" t="inlineStr">
+        <is>
+          <t>configurable Track Model stored in database</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Module/Function</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Output Destination</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Output Name</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Output Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="39">
+        <f>B1</f>
+        <v/>
+      </c>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>Commanded Speed</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="inlineStr">
+        <is>
+          <t>int m/s</t>
+        </is>
+      </c>
+      <c r="E27" s="41" t="inlineStr">
+        <is>
+          <t>Commanded speed of the occupied block, in whole m/s, delivered via the track circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39">
+        <f>A27</f>
+        <v/>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>block_id</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="inlineStr">
+        <is>
+          <t>Authority of the occupied block, delivered via the track circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39">
+        <f>A28</f>
+        <v/>
+      </c>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>Beacon</t>
+        </is>
+      </c>
+      <c r="D29" s="40" t="inlineStr">
+        <is>
+          <t>struct</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="inlineStr">
+        <is>
+          <t>Station name, platform side (L/R, LR = both), and underground flag. Sent on blocks next to a station; none elsewhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39">
+        <f>A29</f>
+        <v/>
+      </c>
+      <c r="B30" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>Block ID</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>block_id</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>Block the train occupies</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A31" s="39">
+        <f>A30</f>
+        <v/>
+      </c>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>Grade of the occupied block, used in Newton-law motion model</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39">
+        <f>A31</f>
+        <v/>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>Elevation</t>
+        </is>
+      </c>
+      <c r="D32" s="40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E32" s="41" t="inlineStr">
+        <is>
+          <t>Elevation of the occupied block above datum</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39">
+        <f>A32</f>
+        <v/>
+      </c>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Speed Limit</t>
+        </is>
+      </c>
+      <c r="D33" s="40" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Speed command to encode into the block track circuit signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="6">
-      <c r="A9" s="23">
-        <f>B1</f>
-        <v/>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>Speed limit of the occupied block</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39">
+        <f>A33</f>
+        <v/>
+      </c>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>Block Polarity</t>
+        </is>
+      </c>
+      <c r="D34" s="40" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>Track circuit polarity. Reverses at every block change so the Train Model can detect it</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39">
+        <f>A34</f>
+        <v/>
+      </c>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Station Name</t>
+        </is>
+      </c>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>string or none</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>Station in the occupied block, if any</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39">
+        <f>A35</f>
+        <v/>
+      </c>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>Train Model</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Passengers Boarded</t>
+        </is>
+      </c>
+      <c r="D36" s="40" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>Passengers boarding while the train is stopped at a station; at most its reported Passenger Capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39">
+        <f>A36</f>
+        <v/>
+      </c>
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>SW Track Controller</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Authority</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Maximum permitted travel distance to encode into track circuit</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="6">
-      <c r="A10" s="24">
-        <f>A9</f>
-        <v/>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>Block Occupancy</t>
+        </is>
+      </c>
+      <c r="D37" s="40" t="inlineStr">
+        <is>
+          <t>bool (per block)</t>
+        </is>
+      </c>
+      <c r="E37" s="41" t="inlineStr">
+        <is>
+          <t>Occupied flag per block, from each train's position; a failed block also reads occupied. Relayed to the CTC Office by the Track Controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39">
+        <f>A37</f>
+        <v/>
+      </c>
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>SW Track Controller</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Switch Position Command</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Switch States</t>
+        </is>
+      </c>
+      <c r="D38" s="40" t="inlineStr">
         <is>
           <t>enum (Normal/Reverse)</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Commanded position for each switch machine</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="6">
-      <c r="A11" s="24">
-        <f>A10</f>
-        <v/>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>Actual position of each switch machine after executing commands</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39">
+        <f>A38</f>
+        <v/>
+      </c>
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>SW Track Controller</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Signal Light Color</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>enum (Green/Yellow/Red)</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Colour to display on each wayside signal light</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="6">
-      <c r="A12" s="24">
-        <f>A11</f>
-        <v/>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Train Model</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Train Position</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>block_id, offset (m)</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Block ID and metre-offset of the train for occupancy detection</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="6">
-      <c r="A13" s="24">
-        <f>A12</f>
-        <v/>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Environment (UI)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Ambient Temperature</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>degrees F</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Outside air temperature used to control the track heater</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="1" s="6">
-      <c r="A14" s="24">
-        <f>A13</f>
-        <v/>
-      </c>
-      <c r="E14" s="14" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="6">
-      <c r="A15" s="24">
-        <f>A14</f>
-        <v/>
-      </c>
-      <c r="E15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A16" s="25">
-        <f>A9</f>
-        <v/>
-      </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="16.15" customHeight="1" thickBot="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Module/Function</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Output Destination</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Output Name</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Output Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="4.9" customHeight="1" thickBot="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>SW Track Controller / CTC</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Block Occupancy</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>bool (per block)</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Occupied flag per block derived from track circuit presence detection</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30.75" customHeight="1">
-      <c r="A21" s="16">
-        <f>B1</f>
-        <v/>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Train Model</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Commanded Speed</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>Speed command delivered to the train via the track circuit</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19">
-        <f>A21</f>
-        <v/>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Train Model</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Authority</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Maximum travel distance delivered to the train via track circuit</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19">
-        <f>A22</f>
-        <v/>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Train Model</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Beacon</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>struct</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>Next station name, platform side (L/R), and underground flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="19">
-        <f>A23</f>
-        <v/>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SW Track Controller / CTC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Switch States</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>enum (Normal/Reverse)</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>Actual position of each switch machine after executing commands</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19">
-        <f>A24</f>
-        <v/>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SW Track Controller / CTC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>Signal Light States</t>
+        </is>
+      </c>
+      <c r="D39" s="40" t="inlineStr">
+        <is>
+          <t>enum (Green/Yellow/Red/SuperGreen)</t>
+        </is>
+      </c>
+      <c r="E39" s="41" t="inlineStr">
+        <is>
+          <t>Colour each wayside signal light is showing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39">
+        <f>A39</f>
+        <v/>
+      </c>
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
         <is>
           <t>Crossing States</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D40" s="40" t="inlineStr">
         <is>
           <t>bool (gate closed)</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E40" s="41" t="inlineStr">
         <is>
           <t>Whether each railway crossing gate is currently closed</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19">
-        <f>A25</f>
-        <v/>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SW Track Controller / CTC</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="39">
+        <f>A40</f>
+        <v/>
+      </c>
+      <c r="B41" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
         <is>
           <t>Failure Status</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Active failure mode per block (broken rail, circuit, power)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19">
-        <f>A26</f>
-        <v/>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Train Model</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>degrees</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>Grade of the occupied block, used in Newton-law motion model</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19">
-        <f>A27</f>
-        <v/>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Train Model</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Elevation</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>Elevation of the occupied block above datum</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="19">
-        <f>A28</f>
-        <v/>
-      </c>
-      <c r="E29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19">
-        <f>A29</f>
-        <v/>
-      </c>
-      <c r="E30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A31" s="22">
-        <f>A30</f>
-        <v/>
-      </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="10" t="n"/>
+      <c r="D41" s="40" t="inlineStr">
+        <is>
+          <t>enum (per block)</t>
+        </is>
+      </c>
+      <c r="E41" s="41" t="inlineStr">
+        <is>
+          <t>Active failure mode per block (broken rail, circuit, power). Any failure reads the block as occupied and cuts its track circuit; power also holds the switch, turns the light red, drops the gates and stops the section's heaters</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39">
+        <f>A41</f>
+        <v/>
+      </c>
+      <c r="B42" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>Heater State</t>
+        </is>
+      </c>
+      <c r="D42" s="40" t="inlineStr">
+        <is>
+          <t>bool (on/off, per section)</t>
+        </is>
+      </c>
+      <c r="E42" s="41" t="inlineStr">
+        <is>
+          <t>Whether each section's heaters are actually running (off during a power failure in that section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39">
+        <f>A42</f>
+        <v/>
+      </c>
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>Ticket Sales</t>
+        </is>
+      </c>
+      <c r="D43" s="40" t="inlineStr">
+        <is>
+          <t>int (per station)</t>
+        </is>
+      </c>
+      <c r="E43" s="41" t="inlineStr">
+        <is>
+          <t>Tickets sold since the last tick. Relayed to the CTC Office by the Track Controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39">
+        <f>A43</f>
+        <v/>
+      </c>
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>Train Controller</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>Signal Seen</t>
+        </is>
+      </c>
+      <c r="D44" s="40" t="inlineStr">
+        <is>
+          <t>enum or none (per train)</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="inlineStr">
+        <is>
+          <t>Colour of the light a train passes, sent only on the tick it enters that block; the Train Controller keeps it. Pending Train Controller agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39">
+        <f>A44</f>
+        <v/>
+      </c>
+      <c r="B45" s="40" t="inlineStr">
+        <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>Track Temperature</t>
+        </is>
+      </c>
+      <c r="D45" s="40" t="inlineStr">
+        <is>
+          <t>degrees C (per section)</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="inlineStr">
+        <is>
+          <t>Track temperature of each section: ambient, raised while the section's heaters run</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="39">
+        <f>A45</f>
+        <v/>
+      </c>
+      <c r="B46" s="40" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>Track Model</t>
+        </is>
+      </c>
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="inlineStr">
+        <is>
+          <t>configurable Track Model stored in database</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/documents/Project_Information/Architecture & Interface Dictionary.xlsx
+++ b/documents/Project_Information/Architecture & Interface Dictionary.xlsx
@@ -1961,7 +1961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="26.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="D10" s="40" t="inlineStr">
         <is>
-          <t>block_id (per block)</t>
+          <t>int blocks (per block)</t>
         </is>
       </c>
       <c r="E10" s="41" t="inlineStr">
         <is>
-          <t>Block up to which a train in this block may travel; encoded into the block's track circuit</t>
+          <t>How many blocks past its current one a train in this block may still enter (0 = stop); encoded into the block's track circuit</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E15" s="41" t="inlineStr">
         <is>
-          <t>Block and metre-offset into it. Offset &gt;= block length moves the train to the next block along the current switch positions; a negative offset moves it back. Drives block occupancy</t>
+          <t>Block and metres travelled since entering it (the Train Model restarts it at 0 in each block; the Track Model carries the overshoot). Crossing the block's end moves the train on along the current switch positions; going below 0 rolls it back. Drives block occupancy</t>
         </is>
       </c>
     </row>
@@ -2325,22 +2325,22 @@
       </c>
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>Environment (UI)</t>
+          <t>Train Model</t>
         </is>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
-          <t>Ambient Temperature</t>
+          <t>Door State</t>
         </is>
       </c>
       <c r="D19" s="40" t="inlineStr">
         <is>
-          <t>degrees C</t>
+          <t>bool (per train)</t>
         </is>
       </c>
       <c r="E19" s="41" t="inlineStr">
         <is>
-          <t>Outside air temperature used to control the track heater (entered in degrees F on the UI)</t>
+          <t>Whether a left or right door is open; passengers board only with a door open, the rule the Train Model accepts them by</t>
         </is>
       </c>
     </row>
@@ -2356,17 +2356,17 @@
       </c>
       <c r="C20" s="40" t="inlineStr">
         <is>
-          <t>Track Layout</t>
+          <t>Ambient Temperature</t>
         </is>
       </c>
       <c r="D20" s="40" t="inlineStr">
         <is>
-          <t>JSON file</t>
+          <t>degrees C</t>
         </is>
       </c>
       <c r="E20" s="41" t="inlineStr">
         <is>
-          <t>Line layout loaded at startup: blocks, length, grade (%), speed limit (km/h), elevation, stations, switches, crossings, and the direction of travel per block (next_blocks). Converted to degrees and m/s on read</t>
+          <t>Outside air temperature used to control the track heater (entered in degrees F on the UI)</t>
         </is>
       </c>
     </row>
@@ -2377,22 +2377,22 @@
       </c>
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>Track Model UI (Murphy)</t>
+          <t>Environment (UI)</t>
         </is>
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
-          <t>Block Failure</t>
+          <t>Track Layout</t>
         </is>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
-          <t>enum (None/Broken Rail/Track Circuit/Power)</t>
+          <t>JSON file</t>
         </is>
       </c>
       <c r="E21" s="41" t="inlineStr">
         <is>
-          <t>Failure injected on a block from the Track Model UI</t>
+          <t>Line layout loaded at startup: blocks, length, grade (%), speed limit (km/h), elevation, stations, switches, crossings, and the direction of travel per block (next_blocks). Converted to degrees and m/s on read</t>
         </is>
       </c>
     </row>
@@ -2403,84 +2403,84 @@
       </c>
       <c r="B22" s="40" t="inlineStr">
         <is>
+          <t>Track Model UI (Murphy)</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>Block Failure</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="inlineStr">
+        <is>
+          <t>enum (None/Broken Rail/Track Circuit/Power)</t>
+        </is>
+      </c>
+      <c r="E22" s="41" t="inlineStr">
+        <is>
+          <t>Failure injected on a block from the Track Model UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39">
+        <f>A22</f>
+        <v/>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
           <t>"Database"</t>
         </is>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>Track Model</t>
         </is>
       </c>
-      <c r="D22" s="40" t="inlineStr">
+      <c r="D23" s="40" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E22" s="41" t="inlineStr">
+      <c r="E23" s="41" t="inlineStr">
         <is>
           <t>configurable Track Model stored in database</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Module/Function</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Output Destination</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Output Name</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Output Description</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="39">
-        <f>B1</f>
-        <v/>
-      </c>
-      <c r="B27" s="40" t="inlineStr">
-        <is>
-          <t>Train Model</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>Commanded Speed</t>
-        </is>
-      </c>
-      <c r="D27" s="40" t="inlineStr">
-        <is>
-          <t>int m/s</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="inlineStr">
-        <is>
-          <t>Commanded speed of the occupied block, in whole m/s, delivered via the track circuit</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="39">
-        <f>A27</f>
+        <f>B1</f>
         <v/>
       </c>
       <c r="B28" s="40" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Authority</t>
+          <t>Commanded Speed</t>
         </is>
       </c>
       <c r="D28" s="40" t="inlineStr">
         <is>
-          <t>block_id</t>
+          <t>int m/s</t>
         </is>
       </c>
       <c r="E28" s="41" t="inlineStr">
         <is>
-          <t>Authority of the occupied block, delivered via the track circuit</t>
+          <t>Commanded speed of the occupied block, in whole m/s, delivered via the track circuit</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>Beacon</t>
+          <t>Authority</t>
         </is>
       </c>
       <c r="D29" s="40" t="inlineStr">
         <is>
-          <t>struct</t>
+          <t>int blocks</t>
         </is>
       </c>
       <c r="E29" s="41" t="inlineStr">
         <is>
-          <t>Station name, platform side (L/R, LR = both), and underground flag. Sent on blocks next to a station; none elsewhere</t>
+          <t>Authority of the occupied block, a count of blocks (0 = stop), delivered via the track circuit</t>
         </is>
       </c>
     </row>
@@ -2542,17 +2542,17 @@
       </c>
       <c r="C30" s="40" t="inlineStr">
         <is>
-          <t>Block ID</t>
+          <t>Beacon</t>
         </is>
       </c>
       <c r="D30" s="40" t="inlineStr">
         <is>
-          <t>block_id</t>
+          <t>struct</t>
         </is>
       </c>
       <c r="E30" s="41" t="inlineStr">
         <is>
-          <t>Block the train occupies</t>
+          <t>Station name, platform side (L/R, LR = both), and underground flag. Sent on blocks next to a station; none elsewhere</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>Block ID</t>
         </is>
       </c>
       <c r="D31" s="40" t="inlineStr">
         <is>
-          <t>degrees</t>
+          <t>block_id</t>
         </is>
       </c>
       <c r="E31" s="41" t="inlineStr">
         <is>
-          <t>Grade of the occupied block, used in Newton-law motion model</t>
+          <t>Block the train occupies</t>
         </is>
       </c>
     </row>
@@ -2594,17 +2594,17 @@
       </c>
       <c r="C32" s="40" t="inlineStr">
         <is>
-          <t>Elevation</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="D32" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>degrees</t>
         </is>
       </c>
       <c r="E32" s="41" t="inlineStr">
         <is>
-          <t>Elevation of the occupied block above datum</t>
+          <t>Grade of the occupied block, used in Newton-law motion model</t>
         </is>
       </c>
     </row>
@@ -2620,17 +2620,17 @@
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
-          <t>Speed Limit</t>
+          <t>Elevation</t>
         </is>
       </c>
       <c r="D33" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E33" s="41" t="inlineStr">
         <is>
-          <t>Speed limit of the occupied block</t>
+          <t>Elevation of the occupied block above datum</t>
         </is>
       </c>
     </row>
@@ -2646,17 +2646,17 @@
       </c>
       <c r="C34" s="40" t="inlineStr">
         <is>
-          <t>Block Polarity</t>
+          <t>Speed Limit</t>
         </is>
       </c>
       <c r="D34" s="40" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="E34" s="41" t="inlineStr">
         <is>
-          <t>Track circuit polarity. Reverses at every block change so the Train Model can detect it</t>
+          <t>Speed limit of the occupied block</t>
         </is>
       </c>
     </row>
@@ -2672,17 +2672,17 @@
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
-          <t>Station Name</t>
+          <t>Block Polarity</t>
         </is>
       </c>
       <c r="D35" s="40" t="inlineStr">
         <is>
-          <t>string or none</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="E35" s="41" t="inlineStr">
         <is>
-          <t>Station in the occupied block, if any</t>
+          <t>Track circuit polarity. Reverses at every block change so the Train Model can detect it</t>
         </is>
       </c>
     </row>
@@ -2698,17 +2698,17 @@
       </c>
       <c r="C36" s="40" t="inlineStr">
         <is>
-          <t>Passengers Boarded</t>
+          <t>Station Name</t>
         </is>
       </c>
       <c r="D36" s="40" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string or none</t>
         </is>
       </c>
       <c r="E36" s="41" t="inlineStr">
         <is>
-          <t>Passengers boarding while the train is stopped at a station; at most its reported Passenger Capacity</t>
+          <t>Station in the occupied block, if any</t>
         </is>
       </c>
     </row>
@@ -2719,22 +2719,22 @@
       </c>
       <c r="B37" s="40" t="inlineStr">
         <is>
-          <t>SW Track Controller</t>
+          <t>Train Model</t>
         </is>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
-          <t>Block Occupancy</t>
+          <t>Passengers Boarded</t>
         </is>
       </c>
       <c r="D37" s="40" t="inlineStr">
         <is>
-          <t>bool (per block)</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E37" s="41" t="inlineStr">
         <is>
-          <t>Occupied flag per block, from each train's position; a failed block also reads occupied. Relayed to the CTC Office by the Track Controller</t>
+          <t>Passengers boarding while the train is stopped at a station; at most its reported Passenger Capacity</t>
         </is>
       </c>
     </row>
@@ -2750,17 +2750,17 @@
       </c>
       <c r="C38" s="40" t="inlineStr">
         <is>
-          <t>Switch States</t>
+          <t>Block Occupancy</t>
         </is>
       </c>
       <c r="D38" s="40" t="inlineStr">
         <is>
-          <t>enum (Normal/Reverse)</t>
+          <t>bool (per block)</t>
         </is>
       </c>
       <c r="E38" s="41" t="inlineStr">
         <is>
-          <t>Actual position of each switch machine after executing commands</t>
+          <t>Occupied flag per block, from each train's position; a failed block also reads occupied. Relayed to the CTC Office by the Track Controller</t>
         </is>
       </c>
     </row>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
-          <t>Signal Light States</t>
+          <t>Switch States</t>
         </is>
       </c>
       <c r="D39" s="40" t="inlineStr">
         <is>
-          <t>enum (Green/Yellow/Red/SuperGreen)</t>
+          <t>enum (Normal/Reverse)</t>
         </is>
       </c>
       <c r="E39" s="41" t="inlineStr">
         <is>
-          <t>Colour each wayside signal light is showing</t>
+          <t>Actual position of each switch machine after executing commands</t>
         </is>
       </c>
     </row>
@@ -2802,17 +2802,17 @@
       </c>
       <c r="C40" s="40" t="inlineStr">
         <is>
-          <t>Crossing States</t>
+          <t>Signal Light States</t>
         </is>
       </c>
       <c r="D40" s="40" t="inlineStr">
         <is>
-          <t>bool (gate closed)</t>
+          <t>enum (Green/Yellow/Red/SuperGreen)</t>
         </is>
       </c>
       <c r="E40" s="41" t="inlineStr">
         <is>
-          <t>Whether each railway crossing gate is currently closed</t>
+          <t>Colour each wayside signal light is showing</t>
         </is>
       </c>
     </row>
@@ -2828,17 +2828,17 @@
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
-          <t>Failure Status</t>
+          <t>Crossing States</t>
         </is>
       </c>
       <c r="D41" s="40" t="inlineStr">
         <is>
-          <t>enum (per block)</t>
+          <t>bool (gate closed)</t>
         </is>
       </c>
       <c r="E41" s="41" t="inlineStr">
         <is>
-          <t>Active failure mode per block (broken rail, circuit, power). Any failure reads the block as occupied and cuts its track circuit; power also holds the switch, turns the light red, drops the gates and stops the section's heaters</t>
+          <t>Whether each railway crossing gate is currently closed</t>
         </is>
       </c>
     </row>
@@ -2854,17 +2854,17 @@
       </c>
       <c r="C42" s="40" t="inlineStr">
         <is>
-          <t>Heater State</t>
+          <t>Failure Status</t>
         </is>
       </c>
       <c r="D42" s="40" t="inlineStr">
         <is>
-          <t>bool (on/off, per section)</t>
+          <t>enum (per block)</t>
         </is>
       </c>
       <c r="E42" s="41" t="inlineStr">
         <is>
-          <t>Whether each section's heaters are actually running (off during a power failure in that section)</t>
+          <t>Active failure mode per block (broken rail, circuit, power). Any failure reads the block as occupied and cuts its track circuit; power also holds the switch, turns the light red, drops the gates and stops the section's heaters</t>
         </is>
       </c>
     </row>
@@ -2880,17 +2880,17 @@
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
-          <t>Ticket Sales</t>
+          <t>Heater State</t>
         </is>
       </c>
       <c r="D43" s="40" t="inlineStr">
         <is>
-          <t>int (per station)</t>
+          <t>bool (on/off, per section)</t>
         </is>
       </c>
       <c r="E43" s="41" t="inlineStr">
         <is>
-          <t>Tickets sold since the last tick. Relayed to the CTC Office by the Track Controller</t>
+          <t>Whether each section's heaters are actually running (off during a power failure in that section)</t>
         </is>
       </c>
     </row>
@@ -2901,22 +2901,22 @@
       </c>
       <c r="B44" s="40" t="inlineStr">
         <is>
-          <t>Train Controller</t>
+          <t>SW Track Controller</t>
         </is>
       </c>
       <c r="C44" s="40" t="inlineStr">
         <is>
-          <t>Signal Seen</t>
+          <t>Ticket Sales</t>
         </is>
       </c>
       <c r="D44" s="40" t="inlineStr">
         <is>
-          <t>enum or none (per train)</t>
+          <t>int (per station)</t>
         </is>
       </c>
       <c r="E44" s="41" t="inlineStr">
         <is>
-          <t>Colour of the light a train passes, sent only on the tick it enters that block; the Train Controller keeps it. Pending Train Controller agreement</t>
+          <t>Tickets sold since the last tick. Relayed to the CTC Office by the Track Controller</t>
         </is>
       </c>
     </row>
@@ -2927,22 +2927,22 @@
       </c>
       <c r="B45" s="40" t="inlineStr">
         <is>
-          <t>SW Track Controller</t>
+          <t>Train Controller</t>
         </is>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
-          <t>Track Temperature</t>
+          <t>Signal Seen</t>
         </is>
       </c>
       <c r="D45" s="40" t="inlineStr">
         <is>
-          <t>degrees C (per section)</t>
+          <t>enum or none (per train)</t>
         </is>
       </c>
       <c r="E45" s="41" t="inlineStr">
         <is>
-          <t>Track temperature of each section: ambient, raised while the section's heaters run</t>
+          <t>Colour of the light a train passes, sent only on the tick it enters that block; the Train Controller keeps it. Pending Train Controller agreement</t>
         </is>
       </c>
     </row>
@@ -2953,20 +2953,46 @@
       </c>
       <c r="B46" s="40" t="inlineStr">
         <is>
+          <t>SW Track Controller</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>Track Temperature</t>
+        </is>
+      </c>
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>degrees C (per section)</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="inlineStr">
+        <is>
+          <t>Track temperature of each section: ambient, raised while the section's heaters run</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39">
+        <f>A46</f>
+        <v/>
+      </c>
+      <c r="B47" s="40" t="inlineStr">
+        <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="C46" s="40" t="inlineStr">
+      <c r="C47" s="40" t="inlineStr">
         <is>
           <t>Track Model</t>
         </is>
       </c>
-      <c r="D46" s="40" t="inlineStr">
+      <c r="D47" s="40" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E46" s="41" t="inlineStr">
+      <c r="E47" s="41" t="inlineStr">
         <is>
           <t>configurable Track Model stored in database</t>
         </is>
